--- a/Employee_Reports_wi48/Nhuel Caguicla Landicho Q0329.xlsx
+++ b/Employee_Reports_wi48/Nhuel Caguicla Landicho Q0329.xlsx
@@ -569,11 +569,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -618,11 +618,11 @@
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-214</v>
+        <v>-217</v>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -667,11 +667,11 @@
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>-125</v>
+        <v>-128</v>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -716,11 +716,11 @@
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-122</v>
+        <v>-125</v>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
@@ -739,9 +739,21 @@
           <t>Procedure For Handling New or Unfamilliar Task (SOPs)</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr"/>
-      <c r="D7" s="4" t="inlineStr"/>
-      <c r="E7" s="4" t="inlineStr"/>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>LSME-IMS-SOP-022</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
           <t>25-Mar-2025</t>
@@ -753,11 +765,11 @@
         </is>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-110</v>
+        <v>-113</v>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -802,11 +814,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -839,11 +851,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
